--- a/excel_files/4f049555-3ac5-4244-ba1a-c7fc6364be63__key_distribution.xlsx
+++ b/excel_files/4f049555-3ac5-4244-ba1a-c7fc6364be63__key_distribution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dagye\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FE5EB8-62C0-4D1B-96AB-F17D7A06ABC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D56BCA-0C7F-4007-A017-896341849F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
   <si>
     <t>Room Number</t>
   </si>
@@ -38,6 +38,495 @@
   </si>
   <si>
     <t>Returned Keys</t>
+  </si>
+  <si>
+    <t>Remy (2024-02-29 03:05:02), Cameron (2024-12-24 19:48:51)</t>
+  </si>
+  <si>
+    <t>Winter (2024-10-28 18:24:32)</t>
+  </si>
+  <si>
+    <t>Cameron (2024-12-28 16:49:04)</t>
+  </si>
+  <si>
+    <t>Logan (2024-01-20 08:53:24), Landry (2025-03-05 06:33:49)</t>
+  </si>
+  <si>
+    <t>Marley (2024-07-01 11:02:42)</t>
+  </si>
+  <si>
+    <t>Quinn (2024-01-24 16:17:57), Skyler (2024-12-14 00:16:33), Elliot (2024-03-17 19:29:37), Riley (2024-07-20 02:29:27), Sage (2024-03-24 23:25:49)</t>
+  </si>
+  <si>
+    <t>Jesse (2024-06-22 21:27:56), Parker (2024-11-02 07:09:43)</t>
+  </si>
+  <si>
+    <t>Landry (2024-09-15 20:20:20)</t>
+  </si>
+  <si>
+    <t>Winter (2024-04-06 22:13:18)</t>
+  </si>
+  <si>
+    <t>Remy (2025-04-07 09:13:15), Payton (2024-05-08 17:24:41)</t>
+  </si>
+  <si>
+    <t>Riley (2024-07-14 09:23:25)</t>
+  </si>
+  <si>
+    <t>Finley (2025-03-12 14:42:26), Marley (2024-03-07 06:29:28), Riley (2024-10-16 20:36:53), Hayden (2024-09-10 23:21:20)</t>
+  </si>
+  <si>
+    <t>Winter (2025-04-13 06:30:05)</t>
+  </si>
+  <si>
+    <t>Toby (2025-03-17 21:06:04)</t>
+  </si>
+  <si>
+    <t>Payton (2024-08-15 17:04:24), Rowan (2025-04-24 01:01:49)</t>
+  </si>
+  <si>
+    <t>Leslie (2024-10-20 02:13:29), Jamie (2024-05-31 07:28:50)</t>
+  </si>
+  <si>
+    <t>Sage (2024-03-19 12:11:47)</t>
+  </si>
+  <si>
+    <t>Landry (2024-07-14 13:14:20), Taylor (2024-01-22 05:38:27)</t>
+  </si>
+  <si>
+    <t>Sawyer (2024-08-22 18:41:34), Jesse (2024-02-07 05:40:43)</t>
+  </si>
+  <si>
+    <t>Reese (2024-12-16 00:50:17), Jesse (2025-02-11 04:12:11)</t>
+  </si>
+  <si>
+    <t>Payton (2024-09-02 22:20:39), Blake (2024-03-08 00:08:18)</t>
+  </si>
+  <si>
+    <t>Remy (2025-03-29 19:35:45), Logan (2024-05-10 20:17:22), Leslie (2024-01-13 09:41:20), Leslie (2024-06-10 21:16:38)</t>
+  </si>
+  <si>
+    <t>Marley (2025-01-12 18:51:19)</t>
+  </si>
+  <si>
+    <t>Quinn (2024-01-31 22:29:23), Riley (2024-01-13 22:07:13)</t>
+  </si>
+  <si>
+    <t>Avery (2024-12-17 09:53:40)</t>
+  </si>
+  <si>
+    <t>Toby (2025-02-15 19:52:37), Leslie (2024-04-06 18:15:27)</t>
+  </si>
+  <si>
+    <t>Morgan (2024-01-31 08:33:00), Oakley (2024-04-04 09:17:50)</t>
+  </si>
+  <si>
+    <t>Emerson (2025-03-23 07:32:47)</t>
+  </si>
+  <si>
+    <t>Quinn (2024-04-28 22:29:13)</t>
+  </si>
+  <si>
+    <t>Rowan (2025-03-16 03:31:34), Avery (2024-01-16 09:20:51)</t>
+  </si>
+  <si>
+    <t>Sawyer (2024-06-15 11:55:46)</t>
+  </si>
+  <si>
+    <t>Sawyer (2024-09-25 05:28:14), Elliot (2024-10-08 11:51:27)</t>
+  </si>
+  <si>
+    <t>Spencer (2024-04-29 01:49:25), Kai (2024-05-08 08:48:58), Elliot (2024-09-01 04:16:05), Spencer (2024-02-20 11:43:10)</t>
+  </si>
+  <si>
+    <t>Skyler (2024-04-03 00:43:47)</t>
+  </si>
+  <si>
+    <t>Jesse (2024-02-06 09:54:11)</t>
+  </si>
+  <si>
+    <t>Landry (2024-10-04 02:08:07)</t>
+  </si>
+  <si>
+    <t>Cameron (2025-01-21 06:45:23)</t>
+  </si>
+  <si>
+    <t>Winter (2024-01-21 13:50:54), Spencer (2024-11-14 13:13:46), Parker (2024-07-07 19:20:29), Skyler (2025-01-21 02:15:02), Alex (2024-04-15 15:17:24)</t>
+  </si>
+  <si>
+    <t>Leslie (2024-05-08 13:37:27), Jamie (2024-02-29 21:15:14), Charlie (2024-12-14 20:29:30)</t>
+  </si>
+  <si>
+    <t>Oakley (2025-04-07 16:54:37)</t>
+  </si>
+  <si>
+    <t>Remy (2024-11-24 20:50:08)</t>
+  </si>
+  <si>
+    <t>Skyler (2024-10-02 07:55:01), Elliot (2024-02-12 05:40:06)</t>
+  </si>
+  <si>
+    <t>Spencer (2025-01-01 14:29:52), Teagan (2024-03-02 01:50:17)</t>
+  </si>
+  <si>
+    <t>Oakley (2025-01-07 15:00:36)</t>
+  </si>
+  <si>
+    <t>Sawyer (2025-04-12 21:22:29)</t>
+  </si>
+  <si>
+    <t>Finley (2025-02-12 00:26:06), Quinn (2024-12-02 08:10:49)</t>
+  </si>
+  <si>
+    <t>Harper (2025-01-12 12:39:26), Alex (2025-01-07 06:01:28)</t>
+  </si>
+  <si>
+    <t>Robin (2024-02-06 12:26:42), Sage (2024-04-09 01:37:08), Casey (2024-07-02 21:09:20), Jamie (2025-01-26 05:40:29)</t>
+  </si>
+  <si>
+    <t>Taylor (2024-06-27 19:50:39), Riley (2024-03-30 12:03:55), Casey (2024-12-28 17:53:50)</t>
+  </si>
+  <si>
+    <t>Marley (2024-02-12 14:21:42)</t>
+  </si>
+  <si>
+    <t>Sage (2024-10-12 20:28:10)</t>
+  </si>
+  <si>
+    <t>Taylor (2025-01-19 02:44:30), Finley (2024-03-28 12:43:20)</t>
+  </si>
+  <si>
+    <t>Remy (2025-03-19 10:16:39)</t>
+  </si>
+  <si>
+    <t>Remy (2024-01-20 14:47:29), Skyler (2024-11-02 11:39:48), Remy (2024-11-26 13:02:44)</t>
+  </si>
+  <si>
+    <t>Dakota (2025-01-19 16:04:29)</t>
+  </si>
+  <si>
+    <t>Reese (2024-12-28 05:57:46), Blake (2024-02-25 07:19:18), Riley (2024-06-11 03:23:23), Reese (2024-07-16 10:56:02)</t>
+  </si>
+  <si>
+    <t>Marley (2024-11-08 05:53:28), Quinn (2024-03-05 02:13:31), Remy (2025-05-01 02:52:47)</t>
+  </si>
+  <si>
+    <t>Jesse (2024-02-26 12:34:18)</t>
+  </si>
+  <si>
+    <t>Cameron (2024-03-23 02:08:37), Alex (2024-03-25 08:04:40)</t>
+  </si>
+  <si>
+    <t>Harper (2024-01-23 21:06:05), Jordan (2024-04-08 11:25:47)</t>
+  </si>
+  <si>
+    <t>Riley (2025-04-05 10:40:12)</t>
+  </si>
+  <si>
+    <t>Payton (2024-04-09 02:07:00), Kai (2024-10-24 19:05:59)</t>
+  </si>
+  <si>
+    <t>Rowan (2024-10-29 05:06:38)</t>
+  </si>
+  <si>
+    <t>Emerson (2024-02-19 17:19:50), Sawyer (2024-03-09 10:24:29), Avery (2024-09-07 01:39:24), Sage (2024-09-09 03:00:57)</t>
+  </si>
+  <si>
+    <t>Winter (2024-08-16 12:26:56)</t>
+  </si>
+  <si>
+    <t>Kai (2025-03-31 11:43:32), Finley (2024-12-08 03:48:33), Drew (2024-07-29 07:29:01), Winter (2025-03-28 00:52:26)</t>
+  </si>
+  <si>
+    <t>Cameron (2025-01-14 03:58:23)</t>
+  </si>
+  <si>
+    <t>Jordan (2025-03-21 10:23:38)</t>
+  </si>
+  <si>
+    <t>Logan (2024-06-14 05:27:30), Winter (2025-02-28 20:07:32), Drew (2024-08-31 03:38:25)</t>
+  </si>
+  <si>
+    <t>Harper (2024-02-10 23:35:39), Drew (2024-09-23 04:52:37), Harper (2024-07-02 14:00:49)</t>
+  </si>
+  <si>
+    <t>Toby (2024-01-05 00:26:22)</t>
+  </si>
+  <si>
+    <t>Frankie (2024-01-07 05:29:38), Sage (2024-07-17 12:07:35)</t>
+  </si>
+  <si>
+    <t>Remy (2024-04-06 18:25:38)</t>
+  </si>
+  <si>
+    <t>Avery (2025-01-04 12:25:36)</t>
+  </si>
+  <si>
+    <t>Robin (2025-01-27 22:56:33)</t>
+  </si>
+  <si>
+    <t>Riley (2024-09-01 08:58:37)</t>
+  </si>
+  <si>
+    <t>Emerson (2024-10-20 00:56:08), Logan (2024-01-11 23:19:58)</t>
+  </si>
+  <si>
+    <t>Harper (2024-05-26 09:32:53), Robin (2024-03-19 22:02:56)</t>
+  </si>
+  <si>
+    <t>Leslie (2024-12-20 05:48:47)</t>
+  </si>
+  <si>
+    <t>Toby (2024-03-29 12:08:18), Kai (2024-06-04 08:46:04)</t>
+  </si>
+  <si>
+    <t>Leslie (2024-03-05 11:37:48), Parker (2024-10-02 06:24:16), Blake (2024-04-28 23:00:13)</t>
+  </si>
+  <si>
+    <t>Emerson (2024-07-28 00:08:58), Reese (2025-01-26 07:46:30)</t>
+  </si>
+  <si>
+    <t>Rowan (2024-09-13 05:31:38), Robin (2024-08-16 04:17:17)</t>
+  </si>
+  <si>
+    <t>Landry (2025-02-09 02:23:16)</t>
+  </si>
+  <si>
+    <t>Sage (2024-01-09 23:04:59)</t>
+  </si>
+  <si>
+    <t>Finley (2024-05-29 11:04:09), Finley (2025-01-15 03:48:34)</t>
+  </si>
+  <si>
+    <t>Emerson (2024-02-05 07:54:50), Hayden (2025-01-26 19:48:58), Casey (2024-05-14 22:27:29)</t>
+  </si>
+  <si>
+    <t>Taylor (2024-02-18 04:28:26), Riley (2024-12-18 17:18:09)</t>
+  </si>
+  <si>
+    <t>Zion (2025-01-27 17:54:25)</t>
+  </si>
+  <si>
+    <t>Skyler (2024-08-21 03:02:27), Robin (2025-01-24 06:25:43), Marley (2025-01-31 01:58:41)</t>
+  </si>
+  <si>
+    <t>Jamie (2024-09-21 21:37:42), Morgan (2025-03-06 12:25:02)</t>
+  </si>
+  <si>
+    <t>Skyler (2024-05-25 04:48:00)</t>
+  </si>
+  <si>
+    <t>Jamie (2025-04-08 09:50:32)</t>
+  </si>
+  <si>
+    <t>Teagan (2024-12-16 07:55:42)</t>
+  </si>
+  <si>
+    <t>Alex (2024-02-18 18:29:34), Frankie (2024-07-11 07:06:00)</t>
+  </si>
+  <si>
+    <t>Avery (2024-03-07 19:52:16)</t>
+  </si>
+  <si>
+    <t>Riley (2025-04-29 15:21:14)</t>
+  </si>
+  <si>
+    <t>Jamie (2025-03-05 22:25:57)</t>
+  </si>
+  <si>
+    <t>Sage (2024-10-06 01:13:38)</t>
+  </si>
+  <si>
+    <t>Jesse (2024-07-24 02:31:14)</t>
+  </si>
+  <si>
+    <t>Skyler (2024-02-07 14:32:07)</t>
+  </si>
+  <si>
+    <t>Emerson (2025-04-07 14:19:51)</t>
+  </si>
+  <si>
+    <t>Zion (2024-01-16 15:58:54)</t>
+  </si>
+  <si>
+    <t>Avery (2025-05-05 20:44:17), Robin (2024-06-14 18:47:26), Remy (2024-02-17 06:50:45), Elliot (2024-10-24 18:43:47)</t>
+  </si>
+  <si>
+    <t>Alex (2024-08-12 00:08:15)</t>
+  </si>
+  <si>
+    <t>Dakota (2024-10-04 19:53:02)</t>
+  </si>
+  <si>
+    <t>Avery (2024-04-28 12:31:31)</t>
+  </si>
+  <si>
+    <t>Spencer (2025-03-29 00:38:12)</t>
+  </si>
+  <si>
+    <t>Cameron (2025-01-03 21:47:04)</t>
+  </si>
+  <si>
+    <t>Elliot (2024-01-26 15:30:06)</t>
+  </si>
+  <si>
+    <t>Morgan (2025-04-27 03:48:45), Sawyer (2025-04-08 22:48:56), Jamie (2024-06-14 13:20:32)</t>
+  </si>
+  <si>
+    <t>Riley (2024-09-12 02:37:28), Remy (2024-02-03 17:21:29), Logan (2024-02-18 18:05:38)</t>
+  </si>
+  <si>
+    <t>Avery (2024-04-01 11:45:28)</t>
+  </si>
+  <si>
+    <t>Harper (2025-03-08 05:19:11), Landry (2024-01-08 02:48:59)</t>
+  </si>
+  <si>
+    <t>Hayden (2024-11-26 21:32:21)</t>
+  </si>
+  <si>
+    <t>Charlie (2024-06-28 21:21:19), Quinn (2024-07-26 00:35:03)</t>
+  </si>
+  <si>
+    <t>Frankie (2024-08-20 13:10:28), Marley (2024-11-15 13:24:25)</t>
+  </si>
+  <si>
+    <t>Leslie (2024-07-17 14:51:25)</t>
+  </si>
+  <si>
+    <t>Winter (2024-06-13 15:29:46)</t>
+  </si>
+  <si>
+    <t>Harper (2024-02-16 11:04:42), Oakley (2024-03-10 08:43:41), Robin (2024-03-22 06:27:49)</t>
+  </si>
+  <si>
+    <t>Rowan (2025-04-26 19:01:16)</t>
+  </si>
+  <si>
+    <t>Jesse (2024-01-17 21:04:16)</t>
+  </si>
+  <si>
+    <t>Logan (2024-07-10 13:08:00), Sage (2025-03-26 22:41:05), Jesse (2024-02-16 20:31:54), Marley (2025-01-15 05:33:21)</t>
+  </si>
+  <si>
+    <t>Skyler (2024-02-18 17:34:40)</t>
+  </si>
+  <si>
+    <t>Jesse (2024-07-08 22:46:52), Emerson (2024-01-20 09:31:12), Sage (2025-03-02 16:41:49), Spencer (2024-08-27 15:55:36), Hayden (2025-02-23 11:17:33)</t>
+  </si>
+  <si>
+    <t>Leslie (2024-03-27 12:56:19), Jamie (2024-07-10 03:16:03)</t>
+  </si>
+  <si>
+    <t>Morgan (2024-09-24 20:40:52)</t>
+  </si>
+  <si>
+    <t>Sage (2024-09-17 16:15:04), Toby (2024-04-28 04:13:54)</t>
+  </si>
+  <si>
+    <t>Elliot (2024-01-12 16:47:06), Oakley (2025-03-25 23:23:32), Remy (2024-12-25 05:53:43)</t>
+  </si>
+  <si>
+    <t>Hayden (2025-01-13 21:35:41)</t>
+  </si>
+  <si>
+    <t>Harper (2025-04-08 14:56:09)</t>
+  </si>
+  <si>
+    <t>Leslie (2025-03-12 23:27:47)</t>
+  </si>
+  <si>
+    <t>Parker (2024-07-18 15:10:39)</t>
+  </si>
+  <si>
+    <t>Marley (2025-02-16 21:35:27), Toby (2024-04-04 01:21:09), Kai (2025-02-24 09:21:36)</t>
+  </si>
+  <si>
+    <t>Toby (2024-07-03 18:05:13)</t>
+  </si>
+  <si>
+    <t>Jesse (2024-01-07 03:21:17)</t>
+  </si>
+  <si>
+    <t>Reese (2024-11-23 11:39:20), Jamie (2025-03-13 10:51:09)</t>
+  </si>
+  <si>
+    <t>Frankie (2024-10-07 21:13:33), Landry (2024-06-30 02:50:34), Toby (2024-04-22 14:23:55), Quinn (2025-04-14 06:28:05)</t>
+  </si>
+  <si>
+    <t>Riley (2024-02-23 21:32:30)</t>
+  </si>
+  <si>
+    <t>Oakley (2025-02-05 21:36:08)</t>
+  </si>
+  <si>
+    <t>Harper (2025-03-13 06:44:45)</t>
+  </si>
+  <si>
+    <t>Jordan (2024-01-13 00:38:57)</t>
+  </si>
+  <si>
+    <t>Morgan (2024-04-26 21:18:04), Spencer (2024-05-30 07:41:38)</t>
+  </si>
+  <si>
+    <t>Marley (2024-09-29 02:06:29), Sawyer (2025-02-14 13:57:32), Payton (2024-10-03 06:17:05), Landry (2024-12-07 22:58:36)</t>
+  </si>
+  <si>
+    <t>Toby (2025-03-11 10:37:57), Marley (2024-10-24 12:12:13), Drew (2025-05-09 01:41:42), Parker (2025-03-31 16:51:02)</t>
+  </si>
+  <si>
+    <t>Riley (2024-06-22 19:35:14), Remy (2024-11-20 06:40:46), Dakota (2024-03-11 19:21:53)</t>
+  </si>
+  <si>
+    <t>Leslie (2024-06-05 11:18:10)</t>
+  </si>
+  <si>
+    <t>Blake (2024-05-02 20:20:04)</t>
+  </si>
+  <si>
+    <t>Frankie (2025-04-06 17:29:37)</t>
+  </si>
+  <si>
+    <t>Sage (2024-04-02 01:11:57)</t>
+  </si>
+  <si>
+    <t>Alex (2025-03-01 12:50:21), Emerson (2024-08-20 19:20:09), Elliot (2024-12-25 13:36:55)</t>
+  </si>
+  <si>
+    <t>Hayden (2024-09-25 14:09:05)</t>
+  </si>
+  <si>
+    <t>Harper (2024-07-25 21:21:12), Winter (2024-02-22 06:11:22), Elliot (2024-01-25 05:56:12)</t>
+  </si>
+  <si>
+    <t>Cameron (2024-04-09 04:44:12), Dakota (2025-02-04 21:44:07)</t>
+  </si>
+  <si>
+    <t>Alex (2024-10-29 04:37:39), Emerson (2024-04-14 16:38:06)</t>
+  </si>
+  <si>
+    <t>Zion (2025-04-17 02:47:06), Elliot (2024-09-12 02:32:50)</t>
+  </si>
+  <si>
+    <t>Hayden (2024-12-09 07:07:35), Skyler (2024-07-10 15:33:44), Winter (2024-06-29 01:02:23)</t>
+  </si>
+  <si>
+    <t>Drew (2024-09-15 16:17:37), Quinn (2024-09-04 07:02:13)</t>
+  </si>
+  <si>
+    <t>Avery (2025-05-04 07:55:54), Marley (2025-02-25 07:48:18), Zion (2024-10-23 01:46:16)</t>
+  </si>
+  <si>
+    <t>Toby (2024-03-24 19:28:44)</t>
+  </si>
+  <si>
+    <t>Hayden (2025-02-05 12:23:26), Toby (2024-12-01 18:49:46), Rowan (2024-07-22 03:09:36), Winter (2024-03-08 07:16:08)</t>
+  </si>
+  <si>
+    <t>Sage (2025-02-28 19:18:50)</t>
+  </si>
+  <si>
+    <t>Hayden (2025-01-07 08:15:09)</t>
   </si>
 </sst>
 </file>
@@ -411,7 +900,13 @@
         <v>101</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -419,7 +914,16 @@
         <v>102</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -435,7 +939,10 @@
         <v>104</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -443,7 +950,16 @@
         <v>105</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -459,7 +975,13 @@
         <v>107</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -467,7 +989,16 @@
         <v>108</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -475,7 +1006,16 @@
         <v>109</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -483,7 +1023,16 @@
         <v>110</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
@@ -499,7 +1048,10 @@
         <v>112</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -515,7 +1067,16 @@
         <v>114</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
@@ -523,10 +1084,13 @@
         <v>115</v>
       </c>
       <c r="B16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>116</v>
       </c>
@@ -534,23 +1098,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>117</v>
       </c>
       <c r="B18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>118</v>
       </c>
       <c r="B19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>119</v>
       </c>
@@ -558,23 +1131,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>120</v>
       </c>
       <c r="B21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>121</v>
       </c>
       <c r="B22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>122</v>
       </c>
@@ -582,15 +1167,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>123</v>
       </c>
       <c r="B24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>124</v>
       </c>
@@ -598,87 +1186,141 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>125</v>
       </c>
       <c r="B26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>126</v>
       </c>
       <c r="B27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>127</v>
       </c>
       <c r="B28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>128</v>
       </c>
       <c r="B29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>129</v>
       </c>
       <c r="B30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>130</v>
       </c>
       <c r="B31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>131</v>
       </c>
       <c r="B32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>132</v>
       </c>
       <c r="B33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>133</v>
       </c>
       <c r="B34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>134</v>
       </c>
       <c r="B35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>135</v>
       </c>
@@ -686,23 +1328,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>136</v>
       </c>
       <c r="B37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>137</v>
       </c>
       <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>138</v>
       </c>
@@ -710,39 +1364,72 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>139</v>
       </c>
       <c r="B40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>140</v>
       </c>
       <c r="B41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" t="s">
+        <v>64</v>
+      </c>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>141</v>
       </c>
       <c r="B42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>142</v>
       </c>
       <c r="B43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>143</v>
       </c>
@@ -750,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>144</v>
       </c>
@@ -758,15 +1445,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>145</v>
       </c>
       <c r="B46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>146</v>
       </c>
@@ -774,15 +1473,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>147</v>
       </c>
       <c r="B48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>148</v>
       </c>
@@ -790,167 +1495,302 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>149</v>
       </c>
       <c r="B50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>150</v>
       </c>
       <c r="B51">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>151</v>
       </c>
       <c r="B52">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>152</v>
       </c>
       <c r="B53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" t="s">
+        <v>84</v>
+      </c>
+      <c r="F53" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>153</v>
       </c>
       <c r="B54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C54" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>154</v>
       </c>
       <c r="B55">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>155</v>
       </c>
       <c r="B56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C56" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" t="s">
+        <v>92</v>
+      </c>
+      <c r="F56" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>156</v>
       </c>
       <c r="B57">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>157</v>
       </c>
       <c r="B58">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" t="s">
+        <v>98</v>
+      </c>
+      <c r="F58" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>158</v>
       </c>
       <c r="B59">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>159</v>
       </c>
       <c r="B60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>101</v>
+      </c>
+      <c r="E60" t="s">
+        <v>102</v>
+      </c>
+      <c r="F60" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>160</v>
       </c>
       <c r="B61">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>104</v>
+      </c>
+      <c r="F61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>161</v>
       </c>
       <c r="B62">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="E62" t="s">
+        <v>106</v>
+      </c>
+      <c r="F62" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>162</v>
       </c>
       <c r="B63">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="E63" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>163</v>
       </c>
       <c r="B64">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>164</v>
       </c>
       <c r="B65">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>111</v>
+      </c>
+      <c r="E65" t="s">
+        <v>112</v>
+      </c>
+      <c r="F65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>165</v>
       </c>
       <c r="B66">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>166</v>
       </c>
       <c r="B67">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="D67" t="s">
+        <v>115</v>
+      </c>
+      <c r="E67" t="s">
+        <v>116</v>
+      </c>
+      <c r="F67" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>167</v>
       </c>
       <c r="B68">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F68" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>168</v>
       </c>
       <c r="B69">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="E69" t="s">
+        <v>121</v>
+      </c>
+      <c r="F69" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>169</v>
       </c>
@@ -958,39 +1798,69 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>170</v>
       </c>
       <c r="B71">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>123</v>
+      </c>
+      <c r="F71" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>171</v>
       </c>
       <c r="B72">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C72" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72" t="s">
+        <v>126</v>
+      </c>
+      <c r="E72" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>172</v>
       </c>
       <c r="B73">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C73" t="s">
+        <v>128</v>
+      </c>
+      <c r="E73" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>173</v>
       </c>
       <c r="B74">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>131</v>
+      </c>
+      <c r="E74" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>174</v>
       </c>
@@ -998,47 +1868,77 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>175</v>
       </c>
       <c r="B76">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D76" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>176</v>
       </c>
       <c r="B77">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="D77" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>177</v>
       </c>
       <c r="B78">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>136</v>
+      </c>
+      <c r="E78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F78" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>178</v>
       </c>
       <c r="B79">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>179</v>
       </c>
       <c r="B80">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>140</v>
+      </c>
+      <c r="E80" t="s">
+        <v>141</v>
+      </c>
+      <c r="F80" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>180</v>
       </c>
@@ -1046,39 +1946,57 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>181</v>
       </c>
       <c r="B82">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>182</v>
       </c>
       <c r="B83">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>183</v>
       </c>
       <c r="B84">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C84" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" t="s">
+        <v>146</v>
+      </c>
+      <c r="E84" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>184</v>
       </c>
       <c r="B85">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C85" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>185</v>
       </c>
@@ -1086,39 +2004,57 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>186</v>
       </c>
       <c r="B87">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>149</v>
+      </c>
+      <c r="F87" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>187</v>
       </c>
       <c r="B88">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="D88" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>188</v>
       </c>
       <c r="B89">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>189</v>
       </c>
       <c r="B90">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="E90" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>190</v>
       </c>
@@ -1126,31 +2062,40 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>191</v>
       </c>
       <c r="B92">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>192</v>
       </c>
       <c r="B93">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="C93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>193</v>
       </c>
       <c r="B94">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>194</v>
       </c>
@@ -1158,39 +2103,66 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>195</v>
       </c>
       <c r="B96">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="D96" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>196</v>
       </c>
       <c r="B97">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="C97" t="s">
+        <v>159</v>
+      </c>
+      <c r="F97" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>197</v>
       </c>
       <c r="B98">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="C98" t="s">
+        <v>161</v>
+      </c>
+      <c r="E98" t="s">
+        <v>162</v>
+      </c>
+      <c r="F98" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>198</v>
       </c>
       <c r="B99">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>164</v>
+      </c>
+      <c r="E99" t="s">
+        <v>165</v>
+      </c>
+      <c r="F99" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>199</v>
       </c>
@@ -1198,12 +2170,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>200</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
+        <v>167</v>
+      </c>
+      <c r="F101" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
